--- a/results/result_evaluation_logs/C_Error_Incorporation_Baseline.xlsx
+++ b/results/result_evaluation_logs/C_Error_Incorporation_Baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -627,11 +622,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>22015cce-aa46-4be9-9520-5baadd8156a0</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -707,11 +697,6 @@
 &lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q120&gt; .
 &lt;http://www.wikidata.org/entity/Q17516&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q20992419&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>b4d0549e-33d5-4a77-9abe-38ad65b33629</t>
         </is>
       </c>
     </row>
@@ -790,11 +775,6 @@
 &lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P184&gt; &lt;http://www.wikidata.org/entity/Q370496&gt; .
 &lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q142&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0d9c1912-e30b-4ab0-b351-46c99f33bf86</t>
         </is>
       </c>
     </row>
@@ -879,11 +859,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5ee3c962-11bd-4aa8-8abf-68338273f2cc</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -958,11 +933,6 @@
 &lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P569&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 &lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>e605119b-abe2-48af-94a1-b18a71e7cf8a</t>
         </is>
       </c>
     </row>
@@ -1045,11 +1015,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>bdae9c36-2bf2-4e7b-b42e-7ba6361e2ca5</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1124,11 +1089,6 @@
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P138&gt; &lt;http://www.wikidata.org/entity/Q28937&gt; .
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>ea8aa4f6-0c66-4c50-b6ee-6da37e462fca</t>
         </is>
       </c>
     </row>
@@ -1212,11 +1172,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3cb52dfb-dff8-424c-a6ca-f7bc768e5742</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1298,11 +1253,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>efc328a3-f7e5-49d5-aabf-a446c4ef02c1</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1383,11 +1333,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>85e17122-05ca-4907-9e6e-41d0f1efc80f</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1465,11 +1410,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>027645c4-a31f-43ac-a30b-328e3a386b91</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1546,11 +1486,6 @@
 </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>a3caa6cf-287d-4304-aaf8-e21e1467b4b3</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1627,11 +1562,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>83fc2944-2c17-4017-b565-e0f8ab2fbc7e</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1671,16 +1601,16 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
@@ -1711,11 +1641,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7e373dad-f5f6-4310-a3fb-a950f2c1e8b8</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1791,11 +1716,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2db5a465-0988-4934-96eb-4857a30380fe</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1870,11 +1790,6 @@
 &lt;http://www.wikidata.org/entity/Q2057199&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q46046&gt; .
 &lt;http://www.wikidata.org/entity/Q2057199&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q234199&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>c15e2bb3-3b1d-4a17-ab7a-831e212ae069</t>
         </is>
       </c>
     </row>
@@ -1955,11 +1870,6 @@
 </t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>fdda442b-cbe9-4971-aef4-02a20dd813c8</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2005,10 +1915,10 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
@@ -2041,11 +1951,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9e67e338-9c44-4604-8d9e-fcc5921488a7</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2119,11 +2024,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q27914&gt;.
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>0c797720-0ac1-4cc9-b92b-eebe5cd0b493</t>
         </is>
       </c>
     </row>
@@ -2212,11 +2112,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4d29e8af-8e33-40d5-a339-fa9771868615</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2293,11 +2188,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>d4b83bee-9809-4dbb-8a33-f9c01304ba15</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2343,10 +2233,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>5</v>
@@ -2379,11 +2269,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>0e325e21-4b2f-4c62-a1c6-fe6dc2460b12</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2460,11 +2345,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>91104e26-550a-4267-9299-d2847de33e8b</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2540,11 +2420,6 @@
 &lt;http://www.wikidata.org/entity/Q220072&gt; &lt;http://www.wikidata.org/entity/P449&gt; &lt;http://www.wikidata.org/entity/Q5554167&gt; .
 &lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q16239205&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>42afad53-a5bb-4577-8da5-7d0db68d9503</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2503,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2b271166-5742-48ba-8ebb-4bec9fa10175</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2710,11 +2580,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>bdfa446d-0ad9-49e2-a402-084792a0a3dd</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2789,11 +2654,6 @@
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .
 &lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>5c637cf1-8ebc-43a2-af2c-ad3f7269adc9</t>
         </is>
       </c>
     </row>
@@ -2877,11 +2737,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>e6564c0e-4e92-4140-b776-2696df18515b</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2927,10 +2782,10 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -2958,11 +2813,6 @@
 &lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q36&gt; .
 &lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q532&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>06769f29-511c-438a-9cc5-4d8ecf6747ed</t>
         </is>
       </c>
     </row>
@@ -3046,11 +2896,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>c6b1142e-7a5e-49e4-9974-095da17fa5a9</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3126,11 +2971,6 @@
 &lt;http://www.wikidata.org/entity/Q64876878&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q262170&gt; .
 &lt;http://www.wikidata.org/entity/Q262170&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q64876878&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>b5d61be4-c731-4fdb-9831-98a5552543a0</t>
         </is>
       </c>
     </row>
@@ -3211,11 +3051,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>01292a6c-a622-4322-94d2-b3a0dc27a1ac</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3294,11 +3129,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2eaa916c-bc77-479f-9f16-a199a95e4aed</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3375,11 +3205,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>963cf0b4-6d6a-4bd8-bec0-3200b0e1fc8c</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3457,11 +3282,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>34607d9b-06ff-4245-9b0c-334fccedb1c4</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3539,11 +3359,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>b88923c3-05bf-40dd-b1ec-96328623bcc0</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3589,10 +3404,10 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
@@ -3621,11 +3436,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>6c4e55ae-b4d1-4d9d-855f-bbf21285977f</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3703,11 +3513,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>4425e85a-69cd-41e2-b537-76c6d4de78d5</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3784,11 +3589,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>1089fee8-7d9e-472d-8759-b68728d81091</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3865,11 +3665,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>b42a8eca-077d-48ea-b214-27f46a5fa8ed</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3909,7 +3704,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
         <v>5</v>
@@ -3951,11 +3746,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>f89e3086-e83b-4674-b9bd-c7d8e0d12489</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4032,11 +3822,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>7e348a8f-4555-4fd8-8534-883ea3f1304b</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4112,11 +3897,6 @@
 &lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q148&gt; .
 &lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P1454&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>3ba50acf-3577-4f36-8445-f0e68ca8a1fe</t>
         </is>
       </c>
     </row>
@@ -4199,11 +3979,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>d6089ee6-c56c-432d-99a3-007aef32d018</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4281,11 +4056,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>464b8723-e6a1-4710-b6a1-24497b6b806b</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4360,11 +4130,6 @@
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q753805&gt; .
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>c018a432-96b5-47e3-a140-4db4478c2590</t>
         </is>
       </c>
     </row>
@@ -4445,11 +4210,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>44cf72dc-2830-490c-919e-c30d3e593fa4</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4489,16 +4249,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -4529,11 +4289,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>6fd3a450-1a9b-42e1-91d0-58b9060b689b</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4579,10 +4334,10 @@
         <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
         <v>4</v>
@@ -4612,11 +4367,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>64d8a5f2-b00f-4759-afa7-b8601c95edda</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4690,11 +4440,6 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt;.
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>e51e228c-9e83-4534-97ff-32d85fca99f2</t>
         </is>
       </c>
     </row>

--- a/results/result_evaluation_logs/C_Error_Incorporation_Baseline.xlsx
+++ b/results/result_evaluation_logs/C_Error_Incorporation_Baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,28 +544,33 @@
           <t>Result String</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Langfuse Trace ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -574,28 +579,28 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -604,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
@@ -615,11 +620,14 @@
       <c r="W2" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q1516254&gt; .
 &lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q364841&gt; .
-&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P264&gt; &lt;http://www.wikidata.org/entity/Q1516254&gt; .
-&lt;http://www.wikidata.org/entity/Q364841&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q25095540&gt; .
-&lt;http://www.wikidata.org/entity/Q25095540&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q8341&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1ab70cd7-c3b0-48f9-9772-048910338231</t>
         </is>
       </c>
     </row>
@@ -643,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -693,10 +701,15 @@
       <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q17516&gt; .
-&lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q120&gt; .
-&lt;http://www.wikidata.org/entity/Q17516&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q20992419&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P1049&gt; &lt;http://www.wikidata.org/entity/Q17516&gt; .
+&lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P5072&gt; &lt;http://www.wikidata.org/entity/Q120&gt; .
+&lt;http://www.wikidata.org/entity/Q20992419&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q20992419&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6c7ea5d8-f265-49a0-bdc0-c898451a2bde</t>
         </is>
       </c>
     </row>
@@ -717,16 +730,16 @@
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -735,22 +748,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>5</v>
@@ -759,22 +772,28 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P184&gt; &lt;http://www.wikidata.org/entity/Q370496&gt; .
 &lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q395&gt; .
-&lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P108&gt; &lt;http://www.wikidata.org/entity/Q273626&gt; .
-&lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P184&gt; &lt;http://www.wikidata.org/entity/Q370496&gt; .
-&lt;http://www.wikidata.org/entity/Q466774&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q142&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q273626&gt; &lt;http://www.wikidata.org/entity/P108&gt; &lt;http://www.wikidata.org/entity/Q466774&gt; .
+&lt;http://www.wikidata.org/entity/Q142&gt; &lt;http://www.wikidata.org/entity/P194&gt; &lt;http://www.wikidata.org/entity/Q632552&gt; .
+&lt;http://www.wikidata.org/entity/Q632552&gt; &lt;http://www.wikidata.org/entity/P194&gt; &lt;http://www.wikidata.org/entity/Q142&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>843612e5-b20f-4200-97f6-5a4ea974542f</t>
         </is>
       </c>
     </row>
@@ -783,22 +802,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -813,50 +832,53 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>8</v>
       </c>
       <c r="U5" t="n">
         <v>7</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q258&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q11424&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P2408&gt; &lt;http://www.wikidata.org/entity/Q81725&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1993848&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P1552&gt; &lt;http://www.wikidata.org/entity/Q4557532&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q4557532&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q723685&gt; .
-&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P569&gt; &lt;http://www.wikidata.org/entity/Q2025690&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q11424&gt; .
+&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P921&gt; &lt;http://www.wikidata.org/entity/Q1993848&gt; .
+&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q723685&gt; .
+&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q258&gt; .
+&lt;http://www.wikidata.org/entity/Q72697912&gt; &lt;http://www.wikidata.org/entity/Q217199&gt; "18 (British Board of Film Classification)" .
+&lt;http://www.wikidata.org/entity/Q81725&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q258&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9508a8d2-37b0-467e-9a3c-e2b3f5e67723</t>
         </is>
       </c>
     </row>
@@ -877,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -889,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -930,9 +952,13 @@
       <c r="W6" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P569&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 &lt;http://www.wikidata.org/entity/Q36771&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q29999&gt; .
 </t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>de8abf2e-0a01-46dc-bf32-8f63ddec642a</t>
         </is>
       </c>
     </row>
@@ -953,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -965,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -992,27 +1018,29 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
         <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q192786&gt; .
+&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q279014&gt; .
+&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P366&gt; &lt;http://www.wikidata.org/entity/Q192786&gt; .
 &lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P366&gt; &lt;http://www.wikidata.org/entity/Q177&gt; .
-&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P176&gt; &lt;http://www.wikidata.org/entity/Q192786&gt; .
-&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q192786&gt; .
-&lt;http://www.wikidata.org/entity/Q192786&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q506252&gt; .
-&lt;http://www.wikidata.org/entity/Q506252&gt; &lt;http://www.wikidata.org/entity/P366&gt; &lt;http://www.wikidata.org/entity/Q192786&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>8063fa08-5f98-445f-a2f6-b2469c58dac7</t>
         </is>
       </c>
     </row>
@@ -1021,19 +1049,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1045,28 +1073,28 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
@@ -1087,8 +1115,14 @@
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P138&gt; &lt;http://www.wikidata.org/entity/Q28937&gt; .
-&lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q65943&gt; .
+&lt;http://www.wikidata.org/entity/Q2226643&gt; &lt;http://www.wikidata.org/entity/P101&gt; &lt;http://www.wikidata.org/entity/Q2226643&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>c1c1a199-08ce-42ea-9d71-0239f3b46e92</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -1121,55 +1155,63 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q2808&gt; .
-&lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q3939773&gt; .
-&lt;http://www.wikidata.org/entity/Q2808&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q2601034&gt; .
+&lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q3939773&gt; .
+&lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q2808&gt; .
+&lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P112&gt; &lt;http://www.wikidata.org/entity/Q2338060&gt; .
+&lt;http://www.wikidata.org/entity/Q2808&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q11399&gt; .
+&lt;http://www.wikidata.org/entity/Q2808&gt; &lt;http://www.wikidata.org/entity/P161&gt; &lt;http://www.wikidata.org/entity/Q2601034&gt; .
+&lt;http://www.wikidata.org/entity/Q2338060&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q2601034&gt; .
 &lt;http://www.wikidata.org/entity/Q3939773&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q2601034&gt; .
 &lt;http://www.wikidata.org/entity/Q2601034&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q2060470&gt; .
-&lt;http://www.wikidata.org/entity/Q2808&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q2060470&gt; .
-&lt;http://www.wikidata.org/entity/Q2060470&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q2808&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q2808&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q11399&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>abe8842d-52b5-4a9e-9287-a1199e42d250</t>
         </is>
       </c>
     </row>
@@ -1178,13 +1220,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -1193,64 +1235,69 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q6782514&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1364658&gt; .
 &lt;http://www.wikidata.org/entity/Q6782514&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q924&gt; .
-&lt;http://www.wikidata.org/entity/Q6782514&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q1773949&gt; .
-&lt;http://www.wikidata.org/entity/Q423&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q1773949&gt; .
-&lt;http://www.wikidata.org/entity/Q7838&gt; &lt;http://www.wikidata.org/entity/P37&gt; &lt;http://www.wikidata.org/entity/Q924&gt; .
+&lt;http://www.wikidata.org/entity/Q6782514&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q6760&gt; .
+&lt;http://www.wikidata.org/entity/Q6760&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1773949&gt; .
 &lt;http://www.wikidata.org/entity/Q924&gt; &lt;http://www.wikidata.org/entity/P37&gt; &lt;http://www.wikidata.org/entity/Q7838&gt; .
+&lt;http://www.wikidata.org/entity/Q924&gt; &lt;http://www.wikidata.org/entity/P530&gt; &lt;http://www.wikidata.org/entity/Q423&gt; .
 &lt;http://www.wikidata.org/entity/Q924&gt; &lt;http://www.wikidata.org/entity/P1906&gt; &lt;http://www.wikidata.org/entity/Q7241291&gt; .
 </t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6e003d32-4a18-46ac-ba0c-bc425d158ee0</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1327,10 @@
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
@@ -1298,39 +1345,44 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
         <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
-&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P91&gt; &lt;http://www.wikidata.org/entity/Q592&gt; .
-&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P26&gt; &lt;http://www.wikidata.org/entity/Q58284&gt; .
-&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q91204&gt; .
-&lt;http://www.wikidata.org/entity/Q58284&gt; &lt;http://www.wikidata.org/entity/P26&gt; &lt;http://www.wikidata.org/entity/Q85563&gt; .
-&lt;http://www.wikidata.org/entity/Q91204&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q85563&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q183&gt;.
+&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P91&gt; &lt;http://www.wikidata.org/entity/Q592&gt;.
+&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P26&gt; &lt;http://www.wikidata.org/entity/Q58284&gt;.
+&lt;http://www.wikidata.org/entity/Q85563&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q91204&gt;.
+&lt;http://www.wikidata.org/entity/Q592&gt; &lt;http://www.wikidata.org/entity/P533&gt; &lt;http://www.wikidata.org/entity/Q24909800&gt;.
+&lt;http://www.wikidata.org/entity/Q24909800&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q43619&gt;.
+</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>49119637-0b25-4e35-94ed-e7f3306e66e0</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1391,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -1369,19 +1421,19 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>3</v>
@@ -1405,9 +1457,14 @@
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q5395743&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q96&gt; .
-&lt;http://www.wikidata.org/entity/Q5395743&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q1321&gt; .
-&lt;http://www.wikidata.org/entity/Q5395743&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q41298&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q5395743&gt; &lt;http://www.wikidata.org/entity/P1416&gt; &lt;http://www.wikidata.org/entity/Q806208&gt; .
+&lt;http://www.wikidata.org/entity/Q5395743&gt; &lt;http://www.wikidata.org/entity/P407&gt; &lt;http://www.wikidata.org/entity/Q1321&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5f413bbe-f96c-4ee1-8eb1-6160b32a282f</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1488,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1446,19 +1503,19 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1467,7 +1524,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
@@ -1481,9 +1538,14 @@
       <c r="W13" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q271108&gt; &lt;http://www.wikidata.org/entity/P710&gt; &lt;http://www.wikidata.org/entity/Q516760&gt; .
 &lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q1605654&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P1344&gt; &lt;http://www.wikidata.org/entity/Q271108&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>d84813c5-17ca-4a9b-8a4d-2cbed893a971</t>
         </is>
       </c>
     </row>
@@ -1492,22 +1554,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -1516,7 +1578,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1537,16 +1599,16 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>3</v>
@@ -1557,9 +1619,17 @@
       <c r="W14" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q7992209&gt; &lt;http://www.wikidata.org/entity/P4661&gt; &lt;http://www.wikidata.org/entity/Q3561541&gt; .
-&lt;http://www.wikidata.org/entity/Q3561541&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q5364109&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q3561541&gt; &lt;http://www.wikidata.org/entity/P287&gt; &lt;http://www.wikidata.org/entity/Q7992209&gt; .
+&lt;http://www.wikidata.org/entity/Q7992209&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q5364109&gt; .
+&lt;http://www.wikidata.org/entity/Q5364109&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q142&gt; .
+&lt;http://www.wikidata.org/entity/Q7992209&gt; &lt;http://www.wikidata.org/entity/P200&gt; &lt;http://www.wikidata.org/entity/Q3561541&gt; .
+&lt;http://www.wikidata.org/entity/Q3561541&gt; &lt;http://www.wikidata.org/entity/P200&gt; &lt;http://www.wikidata.org/entity/Q7992209&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8ca28e09-b669-484b-8805-ee14800a7ca2</t>
         </is>
       </c>
     </row>
@@ -1568,13 +1638,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -1583,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1592,53 +1662,58 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
         <v>4</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q42916999&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q568973&gt; .
-&lt;http://www.wikidata.org/entity/Q142&gt; &lt;http://www.wikidata.org/entity/P5072&gt; &lt;http://www.wikidata.org/entity/Q42916999&gt; .
-&lt;http://www.wikidata.org/entity/Q30&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q568973&gt; .
-&lt;http://www.wikidata.org/entity/Q11696&gt; &lt;http://www.wikidata.org/entity/P1411&gt; &lt;http://www.wikidata.org/entity/Q42916999&gt; .
-&lt;http://www.wikidata.org/entity/Q11696&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q42916999&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q42916999&gt; &lt;http://www.wikidata.org/entity/P156&gt; &lt;http://www.wikidata.org/entity/Q48845659&gt; .
+&lt;http://www.wikidata.org/entity/Q42916999&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q28221935&gt; .
+&lt;http://www.wikidata.org/entity/Q568973&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q42916999&gt; .
+&lt;http://www.wikidata.org/entity/Q48845659&gt; &lt;http://www.wikidata.org/entity/P156&gt; &lt;http://www.wikidata.org/entity/Q42916999&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2c85c9c9-a351-46b0-b4f8-19e2f05ca51c</t>
         </is>
       </c>
     </row>
@@ -1712,8 +1787,13 @@
       <c r="W16" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt;.
-</t>
+&lt;http://www.wikidata.org/entity/Q3311362&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q66117&gt;. 
+</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7cd5a04f-8461-4d7d-97f5-3c5d91d76ce1</t>
         </is>
       </c>
     </row>
@@ -1722,74 +1802,81 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q2057199&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q46046&gt; .
-&lt;http://www.wikidata.org/entity/Q2057199&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q234199&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q7044514&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q46046&gt; .
+&lt;http://www.wikidata.org/entity/Q7044514&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q234199&gt; .
+&lt;http://www.wikidata.org/entity/Q234199&gt; &lt;http://www.wikidata.org/entity/P175&gt; &lt;http://www.wikidata.org/entity/Q7044514&gt; .
+&lt;http://www.wikidata.org/entity/Q7044514&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q134556&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>55655965-83ae-464f-b6dc-272856f9e8b0</t>
         </is>
       </c>
     </row>
@@ -1798,22 +1885,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1822,28 +1909,28 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>3</v>
@@ -1863,11 +1950,15 @@
       <c r="W18" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P5588&gt; &lt;http://www.wikidata.org/entity/Q782&gt; .
 &lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P183&gt; &lt;http://www.wikidata.org/entity/Q664&gt; .
-&lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P5588&gt; &lt;http://www.wikidata.org/entity/Q782&gt; .
-&lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q6933370&gt; .
-&lt;http://www.wikidata.org/entity/Q6933370&gt; &lt;http://www.wikidata.org/entity/P186&gt; &lt;http://www.wikidata.org/entity/Q607380&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q607380&gt; &lt;http://www.wikidata.org/entity/P1672&gt; &lt;http://www.wikidata.org/entity/Q6933370&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>ba3d7f76-ad38-41c9-abdf-952f12e032c0</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1967,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -1906,13 +1997,13 @@
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -1941,14 +2032,19 @@
       <c r="W19" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q794&gt; .
+&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q794&gt; .
 &lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P1012&gt; &lt;http://www.wikidata.org/entity/Q308864&gt; .
 &lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P1012&gt; &lt;http://www.wikidata.org/entity/Q928828&gt; .
-&lt;http://www.wikidata.org/entity/Q5686841&gt; &lt;http://www.wikidata.org/entity/P1012&gt; &lt;http://www.wikidata.org/entity/Q1282219&gt; .
+&lt;http://www.wikidata.org/entity/Q308864&gt; &lt;http://www.wikidata.org/entity/P150&gt; &lt;http://www.wikidata.org/entity/Q1282219&gt; .
 &lt;http://www.wikidata.org/entity/Q308864&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q5686841&gt; .
 &lt;http://www.wikidata.org/entity/Q928828&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q5686841&gt; .
-&lt;http://www.wikidata.org/entity/Q1282219&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q5686841&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q1282219&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q308864&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dedda1ea-20b8-463d-94f8-04c0539e5680</t>
         </is>
       </c>
     </row>
@@ -2026,28 +2122,33 @@
 </t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>62c0db07-a406-4aa1-bbc4-eed3d5b473a0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -2062,7 +2163,7 @@
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
         <v>6</v>
@@ -2077,13 +2178,13 @@
         <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
         <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
         <v>7</v>
@@ -2097,19 +2198,21 @@
       <c r="W21" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
+&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P1412&gt; &lt;http://www.wikidata.org/entity/Q1860&gt; .
+&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P282&gt; &lt;http://www.wikidata.org/entity/Q1860&gt; .
 &lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q82955&gt; .
-&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P19&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P1412&gt; &lt;http://www.wikidata.org/entity/Q1860&gt; .
-&lt;http://www.wikidata.org/entity/Q81056&gt; &lt;http://www.wikidata.org/entity/P2238&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q41549&gt; &lt;http://www.wikidata.org/entity/P237&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
+&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P27&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
+&lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P2238&gt; &lt;http://www.wikidata.org/entity/Q81056&gt; .
+&lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P237&gt; &lt;http://www.wikidata.org/entity/Q41549&gt; .
 &lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P122&gt; &lt;http://www.wikidata.org/entity/Q41614&gt; .
-&lt;http://www.wikidata.org/entity/Q3048624&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q82955&gt; .
-&lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P17&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q1860&gt; &lt;http://www.wikidata.org/entity/P1412&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q81056&gt; &lt;http://www.wikidata.org/entity/P2238&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q81056&gt; &lt;http://www.wikidata.org/entity/Q164800&gt; &lt;http://www.wikidata.org/entity/Q16&gt; .
-&lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P122&gt; &lt;http://www.wikidata.org/entity/Q41614&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q16&gt; &lt;http://www.wikidata.org/entity/P37&gt; &lt;http://www.wikidata.org/entity/Q1860&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>578abfa2-a407-4318-acef-260d429bc658</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2221,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2142,28 +2245,28 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -2172,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
@@ -2183,9 +2286,13 @@
       <c r="W22" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q11348&gt; .
-&lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P101&gt; &lt;http://www.wikidata.org/entity/Q395&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q17052475&gt; &lt;http://www.wikidata.org/entity/P279&gt; &lt;http://www.wikidata.org/entity/Q11348&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>8d7c757f-23da-4ec8-b73d-631e26ddc187</t>
         </is>
       </c>
     </row>
@@ -2206,10 +2313,10 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -2218,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
@@ -2233,13 +2340,13 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
         <v>3</v>
@@ -2248,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>4</v>
@@ -2259,14 +2366,15 @@
       <c r="W23" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q430258&gt; .
+&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q430258&gt; .
 &lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q12174&gt; .
 &lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P703&gt; &lt;http://www.wikidata.org/entity/Q15978631&gt; .
-&lt;http://www.wikidata.org/entity/Q18036690&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .
-&lt;http://www.wikidata.org/entity/Q12174&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q18036690&gt; .
-&lt;http://www.wikidata.org/entity/Q15978631&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q18036690&gt; .
-&lt;http://www.wikidata.org/entity/Q430258&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q18036690&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>c11eec77-217e-4572-94b1-c365449c39a8</t>
         </is>
       </c>
     </row>
@@ -2275,22 +2383,22 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -2299,28 +2407,28 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>2</v>
@@ -2342,7 +2450,16 @@
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .
 &lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P1346&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q1856183&gt; .
+&lt;http://www.wikidata.org/entity/Q188197&gt; &lt;http://www.wikidata.org/entity/P2522&gt; &lt;http://www.wikidata.org/entity/Q674962&gt; .
+&lt;http://www.wikidata.org/entity/Q1856183&gt; &lt;http://www.wikidata.org/entity/P166&gt; &lt;http://www.wikidata.org/entity/Q188197&gt; .
+&lt;http://www.wikidata.org/entity/Q674962&gt; &lt;http://www.wikidata.org/entity/P166&gt; &lt;http://www.wikidata.org/entity/Q188197&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>4b2bd8c0-e21f-45a8-adae-d31fc2c14763</t>
         </is>
       </c>
     </row>
@@ -2351,22 +2468,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -2375,37 +2492,37 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
         <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U25" t="n">
         <v>4</v>
@@ -2416,10 +2533,19 @@
       <c r="W25" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P86&gt; &lt;http://www.wikidata.org/entity/Q16239205&gt; .
 &lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P750&gt; &lt;http://www.wikidata.org/entity/Q520445&gt; .
-&lt;http://www.wikidata.org/entity/Q220072&gt; &lt;http://www.wikidata.org/entity/P449&gt; &lt;http://www.wikidata.org/entity/Q5554167&gt; .
-&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q16239205&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P449&gt; &lt;http://www.wikidata.org/entity/Q220072&gt; .
+&lt;http://www.wikidata.org/entity/Q16239205&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P86&gt; .
+&lt;http://www.wikidata.org/entity/Q520445&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P750&gt; .
+&lt;http://www.wikidata.org/entity/Q220072&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P449&gt; .
+&lt;http://www.wikidata.org/entity/Q5554167&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q11424&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>1ea07f9d-54b4-45a7-be64-d2b8c59f1d2a</t>
         </is>
       </c>
     </row>
@@ -2428,19 +2554,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2452,55 +2578,64 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
         <v>7</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
         <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q664&gt; .
-&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q62066735&gt; .
-&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q62066751&gt; .
-&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P509&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
-&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P509&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P533&gt; &lt;http://www.wikidata.org/entity/Q62066735&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P533&gt; &lt;http://www.wikidata.org/entity/Q62066751&gt; .
 &lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P366&gt; &lt;http://www.wikidata.org/entity/Q486396&gt; .
 &lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P366&gt; &lt;http://www.wikidata.org/entity/Q11244&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P828&gt; &lt;http://www.wikidata.org/entity/Q486296&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P828&gt; &lt;http://www.wikidata.org/entity/Q698752&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q664&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P793&gt; &lt;http://www.wikidata.org/entity/Q62066211&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P5588&gt; &lt;http://www.wikidata.org/entity/Q62066735&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P5588&gt; &lt;http://www.wikidata.org/entity/Q62066751&gt; .
+&lt;http://www.wikidata.org/entity/Q62066211&gt; &lt;http://www.wikidata.org/entity/P793&gt; &lt;http://www.wikidata.org/entity/Q664&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>e2129754-4227-42bd-b26b-ec49dd8bfb96</t>
         </is>
       </c>
     </row>
@@ -2509,22 +2644,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -2533,51 +2668,58 @@
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
         <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U27" t="n">
         <v>5</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q2094579&gt; &lt;http://www.wikidata.org/entity/P138&gt; &lt;http://www.wikidata.org/entity/Q5546527&gt; .
-&lt;http://www.wikidata.org/entity/Q2094579&gt; &lt;http://www.wikidata.org/entity/P50&gt; &lt;http://www.wikidata.org/entity/Q5546527&gt; .
-&lt;http://www.wikidata.org/entity/Q5546527&gt; &lt;http://www.wikidata.org/entity/P138&gt; &lt;http://www.wikidata.org/entity/Q8229&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q2094579&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q827379&gt; .
+&lt;http://www.wikidata.org/entity/Q2094579&gt; &lt;http://www.wikidata.org/entity/P58&gt; &lt;http://www.wikidata.org/entity/Q5546527&gt; .
+&lt;http://www.wikidata.org/entity/Q5546527&gt; &lt;http://www.wikidata.org/entity/P735&gt; &lt;http://www.wikidata.org/entity/Q123829&gt; .
+&lt;http://www.wikidata.org/entity/Q123829&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q8229&gt; .
+&lt;http://www.wikidata.org/entity/Q2094579&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q11424&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>03e1f1be-4f35-4664-8189-4d72ea0cee81</t>
         </is>
       </c>
     </row>
@@ -2656,6 +2798,11 @@
 </t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>f2af092f-ae7a-4779-8cb9-54bfba5a513a</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2674,10 +2821,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -2686,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -2707,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
         <v>5</v>
@@ -2722,19 +2869,26 @@
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q3130&gt; .
-&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q6762533&gt; .
-&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P127&gt; &lt;http://www.wikidata.org/entity/Q8062829&gt; .
-&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q6811747&gt; .
-&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q6762533&gt; .
-&lt;http://www.wikidata.org/entity/Q6811747&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q3130&gt; .
-&lt;http://www.wikidata.org/entity/Q6762533&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q6762533&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q8062829&gt; .
+&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q2060470&gt; .
+&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P1534&gt; &lt;http://www.wikidata.org/entity/Q6811747&gt; .
+&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P1534&gt; &lt;http://www.wikidata.org/entity/Q6762533&gt; .
+&lt;http://www.wikidata.org/entity/Q16926803&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q6811747&gt; .
+&lt;http://www.wikidata.org/entity/Q8062829&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q16926803&gt; .
+&lt;http://www.wikidata.org/entity/Q2060470&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q6811747&gt; .
+&lt;http://www.wikidata.org/entity/Q6811747&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q6811747&gt; .
+&lt;http://www.wikidata.org/entity/Q6762533&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q6762533&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2ae66df0-db14-4880-a0f4-a0a44d927484</t>
         </is>
       </c>
     </row>
@@ -2743,19 +2897,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2773,46 +2927,52 @@
         <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
         <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1840968&gt; .
 &lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q36&gt; .
-&lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q36&gt; .
-&lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q532&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q6723&gt; .
+&lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P421&gt; &lt;http://www.wikidata.org/entity/Q6655&gt; .
+&lt;http://www.wikidata.org/entity/Q8083051&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q484170&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>e59fd970-ddf4-40d8-a5f2-b2b81e166bf3</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2996,7 @@
         <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -2845,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
@@ -2866,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
         <v>3</v>
@@ -2875,7 +3035,7 @@
         <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
         <v>4</v>
@@ -2886,14 +3046,22 @@
       <c r="W31" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
 &lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
 &lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q60&gt; .
 &lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
 &lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P1408&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
-&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P1408&gt; &lt;http://www.wikidata.org/entity/Q60&gt; .
-&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P1408&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
-&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q502319&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P1408&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
+&lt;http://www.wikidata.org/entity/Q304801&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
+&lt;http://www.wikidata.org/entity/Q304801&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q60&gt; .
+&lt;http://www.wikidata.org/entity/Q60&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
+&lt;http://www.wikidata.org/entity/Q14707624&gt; &lt;http://www.wikidata.org/entity/P1408&gt; &lt;http://www.wikidata.org/entity/Q304801&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>57bb4d7f-3673-4585-9e53-0dd0b401f060</t>
         </is>
       </c>
     </row>
@@ -2914,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -2926,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
@@ -2941,10 +3109,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -2970,7 +3138,13 @@
 &lt;http://www.wikidata.org/entity/Q64876878&gt; &lt;http://www.wikidata.org/entity/P674&gt; &lt;http://www.wikidata.org/entity/Q65090308&gt; .
 &lt;http://www.wikidata.org/entity/Q64876878&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q262170&gt; .
 &lt;http://www.wikidata.org/entity/Q262170&gt; &lt;http://www.wikidata.org/entity/P725&gt; &lt;http://www.wikidata.org/entity/Q64876878&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q262170&gt; &lt;http://www.wikidata.org/entity/P161&gt; &lt;http://www.wikidata.org/entity/Q65090308&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>cebd1c1f-3bf9-4f5c-9c92-8caf6d32afc8</t>
         </is>
       </c>
     </row>
@@ -2979,37 +3153,37 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
@@ -3018,37 +3192,45 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
         <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
         <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q1088790&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q190518&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q28&gt; .
-&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P149&gt; &lt;http://www.wikidata.org/entity/Q2722661&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1088790&gt; .
+&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q28&gt; .
+&lt;http://www.wikidata.org/entity/Q1240173&gt; &lt;http://www.wikidata.org/entity/P149&gt; &lt;http://www.wikidata.org/entity/Q46261&gt; .
+&lt;http://www.wikidata.org/entity/Q46261&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q2722661&gt; .
+&lt;http://www.wikidata.org/entity/Q46261&gt; &lt;http://www.wikidata.org/entity/P127&gt; &lt;http://www.wikidata.org/entity/Q202763&gt; .
+&lt;http://www.wikidata.org/entity/Q190518&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q28&gt; .
+&lt;http://www.wikidata.org/entity/Q1088790&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q28&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>bff92c71-2345-4b9c-a085-83a6c23332bf</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3251,7 @@
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -3081,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
@@ -3102,7 +3284,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
         <v>3</v>
@@ -3111,7 +3293,7 @@
         <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
         <v>4</v>
@@ -3122,11 +3304,17 @@
       <c r="W34" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q130232&gt; .
-&lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P161&gt; &lt;http://www.wikidata.org/entity/Q1366759&gt; .
-&lt;http://www.wikidata.org/entity/Q1366759&gt; &lt;http://www.wikidata.org/entity/Q523&gt; &lt;http://www.wikidata.org/entity/Q822946&gt; .
 &lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P2408&gt; &lt;http://www.wikidata.org/entity/Q2644&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q130232&gt; .
+&lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/Q523&gt; &lt;http://www.wikidata.org/entity/Q1366759&gt; .
+&lt;http://www.wikidata.org/entity/Q822946&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q11424&gt; .
+&lt;http://www.wikidata.org/entity/Q1366759&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q822946&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>d58d2db6-7cc0-4efc-ab2f-9512b803c974</t>
         </is>
       </c>
     </row>
@@ -3165,19 +3353,19 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>2</v>
@@ -3200,9 +3388,14 @@
       <c r="W35" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q41792848&gt; &lt;http://www.wikidata.org/entity/P2515&gt; &lt;http://www.wikidata.org/entity/Q5072388&gt; .
-&lt;http://www.wikidata.org/entity/Q41792848&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/Q2515&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q41792848&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P2515&gt; .
+&lt;http://www.wikidata.org/entity/Q41792848&gt; &lt;http://www.wikidata.org/entity/P1441&gt; &lt;http://www.wikidata.org/entity/Q5072388&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>f5efbb1f-2e99-4521-8bfa-b92ad623a020</t>
         </is>
       </c>
     </row>
@@ -3211,10 +3404,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -3241,22 +3434,22 @@
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
@@ -3265,7 +3458,7 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>3</v>
@@ -3276,10 +3469,15 @@
       <c r="W36" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P1433&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
+&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P17&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
 &lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q41298&gt; .
-&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
-&lt;http://www.wikidata.org/entity/Q1490434&gt; &lt;http://www.wikidata.org/entity/P407&gt; &lt;http://www.wikidata.org/entity/Q188&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>772942ad-19a4-48c4-8524-bfd9b1a677dd</t>
         </is>
       </c>
     </row>
@@ -3359,6 +3557,11 @@
 </t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2c4abfc3-b769-4fa6-b136-1aa2fa246f3f</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3368,16 +3571,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -3398,42 +3601,48 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
         <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
         <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q6803534&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1084560&gt; .
 &lt;http://www.wikidata.org/entity/Q6803534&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q1247390&gt; .
-&lt;http://www.wikidata.org/entity/Q6803534&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1320721&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q6803534&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q145&gt; .
+&lt;http://www.wikidata.org/entity/Q6803534&gt; &lt;http://www.wikidata.org/entity/Q8269924&gt; &lt;http://www.wikidata.org/entity/Q1320721&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>3df8f58e-58aa-4390-b909-c1ba60386a81</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3663,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -3466,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
@@ -3475,19 +3684,19 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>2</v>
@@ -3496,7 +3705,7 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>3</v>
@@ -3507,10 +3716,14 @@
       <c r="W39" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P1546&gt; &lt;http://www.wikidata.org/entity/Q877781&gt; .
 &lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q183&gt; .
-&lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q484170&gt; .
-&lt;http://www.wikidata.org/entity/Q907827&gt; &lt;http://www.wikidata.org/entity/P1546&gt; &lt;http://www.wikidata.org/entity/Q877781&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1f74a87e-4c1e-4ae0-b48c-76028d5f426c</t>
         </is>
       </c>
     </row>
@@ -3522,16 +3735,16 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -3543,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -3552,16 +3765,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -3584,9 +3797,13 @@
       <c r="W40" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q1064344&gt; &lt;http://www.wikidata.org/prop/direct/P361&gt; &lt;http://www.wikidata.org/entity/Q1406&gt; .
-&lt;http://www.wikidata.org/entity/Q1064344&gt; &lt;http://www.wikidata.org/prop/direct/P279&gt; &lt;http://www.wikidata.org/entity/Q1406&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q1064344&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1406&gt;.
+</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4a00f5e1-6447-450c-aeab-90dbc2895280</t>
         </is>
       </c>
     </row>
@@ -3595,13 +3812,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3625,19 +3842,19 @@
         <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>2</v>
@@ -3661,8 +3878,13 @@
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P1376&gt; &lt;http://www.wikidata.org/entity/Q54153&gt; .
-&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q1261531&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q47554&gt; &lt;http://www.wikidata.org/entity/P206&gt; &lt;http://www.wikidata.org/entity/Q1261531&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>a0e112a4-4ac6-49df-bd17-b3957dfa80e1</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3893,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
         <v>5</v>
@@ -3683,10 +3905,10 @@
         <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
@@ -3695,55 +3917,61 @@
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
         <v>6</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42" t="n">
         <v>7</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q54322348&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q16568&gt; .
-&lt;http://www.wikidata.org/entity/Q54322348&gt; &lt;http://www.wikidata.org/entity/P17&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
-&lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P6&gt; &lt;http://www.wikidata.org/entity/Q493605&gt; .
+&lt;http://www.wikidata.org/entity/Q54322348&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
+&lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P1376&gt; &lt;http://www.wikidata.org/entity/Q493605&gt; .
+&lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
 &lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P190&gt; &lt;http://www.wikidata.org/entity/Q12191&gt; .
 &lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P190&gt; &lt;http://www.wikidata.org/entity/Q42622&gt; .
-&lt;http://www.wikidata.org/entity/Q54322348&gt; &lt;http://www.wikidata.org/entity/P31&gt; &lt;http://www.wikidata.org/entity/Q41176&gt; .
-&lt;http://www.wikidata.org/entity/Q16568&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q30&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q12191&gt; &lt;http://www.wikidata.org/entity/P190&gt; &lt;http://www.wikidata.org/entity/Q16568&gt; .
+&lt;http://www.wikidata.org/entity/Q42622&gt; &lt;http://www.wikidata.org/entity/P190&gt; &lt;http://www.wikidata.org/entity/Q16568&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>822e8e57-b378-404d-a52b-9d3d91f4556b</t>
         </is>
       </c>
     </row>
@@ -3817,9 +4045,14 @@
       <c r="W43" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q95994024&gt; .
-&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P3373&gt; &lt;http://www.wikidata.org/entity/Q95994024&gt;.
+&lt;http://www.wikidata.org/entity/Q87412161&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q5&gt;.
+</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>ca674ea4-69aa-4937-8fc3-4ac68f60141b</t>
         </is>
       </c>
     </row>
@@ -3840,10 +4073,10 @@
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -3858,19 +4091,19 @@
         <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>3</v>
@@ -3882,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
         <v>3</v>
@@ -3893,10 +4126,16 @@
       <c r="W44" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q1358919&gt; .
-&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q148&gt; .
-&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P1454&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1358919&gt; .
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P1056&gt; &lt;http://www.wikidata.org/entity/Q29644512&gt; .
+&lt;http://www.wikidata.org/entity/Q29644512&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q152074&gt; .
+&lt;http://www.wikidata.org/entity/Q152074&gt; &lt;http://www.wikidata.org/entity/P793&gt; &lt;http://www.wikidata.org/entity/Q29644512&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>aaf40b61-efbe-46b9-84e0-302b23737a53</t>
         </is>
       </c>
     </row>
@@ -3905,78 +4144,84 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
         <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
         <v>9</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
         <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P1672&gt; &lt;http://www.wikidata.org/entity/Q7368&gt; .
+&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P279&gt; &lt;http://www.wikidata.org/entity/Q7368&gt; .
 &lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P495&gt; &lt;http://www.wikidata.org/entity/Q258&gt; .
-&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q7368&gt; .
 &lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q42329&gt; .
-&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q42329&gt; .
-&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/prop/direct/P496&gt; &lt;http://www.wikidata.org/entity/Q651765&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P462&gt; &lt;http://www.wikidata.org/entity/Q23444&gt; .
+&lt;http://www.wikidata.org/entity/Q7368&gt; &lt;http://www.wikidata.org/entity/P162&gt; &lt;http://www.wikidata.org/entity/Q8495&gt; .
+&lt;http://www.wikidata.org/entity/Q5288565&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q7368&gt; .
+&lt;http://www.wikidata.org/entity/Q42329&gt; &lt;http://www.wikidata.org/entity/P186&gt; &lt;http://www.wikidata.org/entity/Q197204&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>7ac87ce0-fa23-44ac-b10c-0f7387289155</t>
         </is>
       </c>
     </row>
@@ -4050,10 +4295,15 @@
       <c r="W46" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q92560&gt; &lt;http://www.wikidata.org/entity/P136&gt; &lt;http://www.wikidata.org/entity/Q231302&gt; .
-&lt;http://www.wikidata.org/entity/Q92560&gt; &lt;http://www.wikidata.org/entity/P8670&gt; &lt;http://www.wikidata.org/entity/Q2061122&gt; .
+&lt;http://www.wikidata.org/entity/Q92560&gt; &lt;http://www.wikidata.org/entity/P287&gt; &lt;http://www.wikidata.org/entity/Q2061122&gt; .
 &lt;http://www.wikidata.org/entity/Q92560&gt; &lt;http://www.wikidata.org/entity/P449&gt; &lt;http://www.wikidata.org/entity/Q734663&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q92560&gt; &lt;http://www.wikidata.org/entity/P2360&gt; &lt;http://www.wikidata.org/entity/Q231302&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>7511f57f-8fbf-4c35-a061-d9f0f7d5785a</t>
         </is>
       </c>
     </row>
@@ -4062,74 +4312,80 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t xml:space="preserve">
 &lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P706&gt; &lt;http://www.wikidata.org/entity/Q753805&gt; .
-&lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P412&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q753805&gt; &lt;http://www.wikidata.org/entity/P279&gt; &lt;http://www.wikidata.org/entity/Q186380&gt; .
+&lt;http://www.wikidata.org/entity/Q18036732&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q7187&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>cf11ffde-0802-4af9-81e4-a73f6df436ed</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -4183,7 +4439,7 @@
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>2</v>
@@ -4203,11 +4459,15 @@
       <c r="W48" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P47&gt; &lt;http://www.wikidata.org/entity/Q979352&gt; .
 &lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
 &lt;http://www.wikidata.org/entity/Q979352&gt; &lt;http://www.wikidata.org/entity/P131&gt; &lt;http://www.wikidata.org/entity/Q112686&gt; .
-&lt;http://www.wikidata.org/entity/Q977911&gt; &lt;http://www.wikidata.org/entity/P47&gt; &lt;http://www.wikidata.org/entity/Q979352&gt; .
-&lt;http://www.wikidata.org/entity/Q979352&gt; &lt;http://www.wikidata.org/entity/P47&gt; &lt;http://www.wikidata.org/entity/Q977911&gt; .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>f0722fbd-27de-44ce-9f87-fabc7446310f</t>
         </is>
       </c>
     </row>
@@ -4216,77 +4476,85 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
         <v>6</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U49" t="n">
         <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P1366&gt; &lt;http://www.wikidata.org/entity/Q170386&gt;.
-&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P156&gt; &lt;http://www.wikidata.org/entity/Q170386&gt;.
-&lt;http://www.wikidata.org/entity/Q170386&gt; &lt;http://www.wikidata.org/entity/P1344&gt; &lt;http://www.wikidata.org/entity/Q4546576&gt;.
-&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P1344&gt; &lt;http://www.wikidata.org/entity/Q4546576&gt;.
-&lt;http://www.wikidata.org/entity/Q170386&gt; &lt;http://www.wikidata.org/entity/P570&gt; &lt;http://www.wikidata.org/entity/Q4546576&gt;.
-</t>
+&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P541&gt; &lt;http://www.wikidata.org/entity/Q19546&gt; .
+&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q173071&gt; .
+&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P527&gt; &lt;http://www.wikidata.org/entity/Q170386&gt; .
+&lt;http://www.wikidata.org/entity/Q4546576&gt; &lt;http://www.wikidata.org/entity/P156&gt; &lt;http://www.wikidata.org/entity/Q1358726&gt; .
+&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P1552&gt; &lt;http://www.wikidata.org/entity/Q5&gt; .
+&lt;http://www.wikidata.org/entity/Q173071&gt; &lt;http://www.wikidata.org/entity/P1535&gt; &lt;http://www.wikidata.org/entity/Q602358&gt; .
+&lt;http://www.wikidata.org/entity/Q170386&gt; &lt;http://www.wikidata.org/entity/P541&gt; &lt;http://www.wikidata.org/entity/Q19546&gt; .
+&lt;http://www.wikidata.org/entity/Q1358726&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q19546&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>289a8a72-ef45-40c6-ad94-ba7322c21f0f</t>
         </is>
       </c>
     </row>
@@ -4295,19 +4563,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -4319,25 +4587,25 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
         <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
         <v>4</v>
@@ -4360,11 +4628,17 @@
       <c r="W50" t="inlineStr">
         <is>
           <t xml:space="preserve">
+&lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1140115&gt; .
+&lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P127&gt; &lt;http://www.wikidata.org/entity/Q4285526&gt; .
+&lt;http://www.wikidata.org/entity/Q4285526&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P1075&gt; .
 &lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q649&gt; .
-&lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P1075&gt; &lt;http://www.wikidata.org/entity/Q4285526&gt; .
-&lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q1140115&gt; .
-&lt;http://www.wikidata.org/entity/Q4285526&gt; &lt;http://www.wikidata.org/entity/P106&gt; &lt;http://www.wikidata.org/entity/P1075&gt; .
-</t>
+&lt;http://www.wikidata.org/entity/Q2822458&gt; &lt;http://www.wikidata.org/entity/P17&gt; &lt;http://www.wikidata.org/entity/Q649&gt; .
+</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>79e466ea-a6f2-4212-af61-102ccd2ebba9</t>
         </is>
       </c>
     </row>
@@ -4373,13 +4647,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -4403,19 +4677,19 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4438,8 +4712,13 @@
       <c r="W51" t="inlineStr">
         <is>
           <t xml:space="preserve">
-&lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P556&gt; &lt;http://www.wikidata.org/entity/Q503601&gt;.
-</t>
+&lt;http://www.wikidata.org/entity/Q2362697&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q503601&gt;.
+</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>bebda8f5-6fa2-4fab-8edc-a7eeee312adb</t>
         </is>
       </c>
     </row>
